--- a/docs/시장 아이템.xlsx
+++ b/docs/시장 아이템.xlsx
@@ -697,15 +697,51 @@
       <c r="P2" s="4" t="inlineStr"/>
       <c r="Q2" s="4" t="inlineStr"/>
       <c r="R2" s="4" t="inlineStr"/>
-      <c r="S2" s="4" t="inlineStr"/>
-      <c r="T2" s="4" t="inlineStr"/>
-      <c r="U2" s="4" t="inlineStr"/>
-      <c r="V2" s="4" t="inlineStr"/>
-      <c r="W2" s="4" t="inlineStr"/>
-      <c r="X2" s="4" t="inlineStr"/>
-      <c r="Y2" s="4" t="inlineStr"/>
-      <c r="Z2" s="4" t="inlineStr"/>
-      <c r="AA2" s="4" t="inlineStr"/>
+      <c r="S2" s="4" t="inlineStr">
+        <is>
+          <t>Herbal Tonic</t>
+        </is>
+      </c>
+      <c r="T2" s="4" t="inlineStr">
+        <is>
+          <t>湯薬</t>
+        </is>
+      </c>
+      <c r="U2" s="4" t="inlineStr">
+        <is>
+          <t>湯藥</t>
+        </is>
+      </c>
+      <c r="V2" s="4" t="inlineStr">
+        <is>
+          <t>汤药</t>
+        </is>
+      </c>
+      <c r="W2" s="4" t="inlineStr">
+        <is>
+          <t>Tônico de Ervas</t>
+        </is>
+      </c>
+      <c r="X2" s="4" t="inlineStr">
+        <is>
+          <t>Tónico de Ervas</t>
+        </is>
+      </c>
+      <c r="Y2" s="4" t="inlineStr">
+        <is>
+          <t>Decotto d'Erbe</t>
+        </is>
+      </c>
+      <c r="Z2" s="4" t="inlineStr">
+        <is>
+          <t>Tónico de Hierbas</t>
+        </is>
+      </c>
+      <c r="AA2" s="4" t="inlineStr">
+        <is>
+          <t>Эмийн тан</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="92" customHeight="1">
       <c r="A3" s="2" t="n">
@@ -756,15 +792,51 @@
       <c r="P3" s="4" t="inlineStr"/>
       <c r="Q3" s="4" t="inlineStr"/>
       <c r="R3" s="4" t="inlineStr"/>
-      <c r="S3" s="4" t="inlineStr"/>
-      <c r="T3" s="4" t="inlineStr"/>
-      <c r="U3" s="4" t="inlineStr"/>
-      <c r="V3" s="4" t="inlineStr"/>
-      <c r="W3" s="4" t="inlineStr"/>
-      <c r="X3" s="4" t="inlineStr"/>
-      <c r="Y3" s="4" t="inlineStr"/>
-      <c r="Z3" s="4" t="inlineStr"/>
-      <c r="AA3" s="4" t="inlineStr"/>
+      <c r="S3" s="4" t="inlineStr">
+        <is>
+          <t>Tea</t>
+        </is>
+      </c>
+      <c r="T3" s="4" t="inlineStr">
+        <is>
+          <t>茶</t>
+        </is>
+      </c>
+      <c r="U3" s="4" t="inlineStr">
+        <is>
+          <t>茶</t>
+        </is>
+      </c>
+      <c r="V3" s="4" t="inlineStr">
+        <is>
+          <t>茶</t>
+        </is>
+      </c>
+      <c r="W3" s="4" t="inlineStr">
+        <is>
+          <t>Chá</t>
+        </is>
+      </c>
+      <c r="X3" s="4" t="inlineStr">
+        <is>
+          <t>Chá</t>
+        </is>
+      </c>
+      <c r="Y3" s="4" t="inlineStr">
+        <is>
+          <t>Tè</t>
+        </is>
+      </c>
+      <c r="Z3" s="4" t="inlineStr">
+        <is>
+          <t>Té</t>
+        </is>
+      </c>
+      <c r="AA3" s="4" t="inlineStr">
+        <is>
+          <t>Цай</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="92" customHeight="1">
       <c r="A4" s="2" t="n">
@@ -815,15 +887,51 @@
       <c r="P4" s="4" t="inlineStr"/>
       <c r="Q4" s="4" t="inlineStr"/>
       <c r="R4" s="4" t="inlineStr"/>
-      <c r="S4" s="4" t="inlineStr"/>
-      <c r="T4" s="4" t="inlineStr"/>
-      <c r="U4" s="4" t="inlineStr"/>
-      <c r="V4" s="4" t="inlineStr"/>
-      <c r="W4" s="4" t="inlineStr"/>
-      <c r="X4" s="4" t="inlineStr"/>
-      <c r="Y4" s="4" t="inlineStr"/>
-      <c r="Z4" s="4" t="inlineStr"/>
-      <c r="AA4" s="4" t="inlineStr"/>
+      <c r="S4" s="4" t="inlineStr">
+        <is>
+          <t>Wooden Ox</t>
+        </is>
+      </c>
+      <c r="T4" s="4" t="inlineStr">
+        <is>
+          <t>木牛流馬</t>
+        </is>
+      </c>
+      <c r="U4" s="4" t="inlineStr">
+        <is>
+          <t>木牛流馬</t>
+        </is>
+      </c>
+      <c r="V4" s="4" t="inlineStr">
+        <is>
+          <t>木牛流马</t>
+        </is>
+      </c>
+      <c r="W4" s="4" t="inlineStr">
+        <is>
+          <t>Boi de Madeira</t>
+        </is>
+      </c>
+      <c r="X4" s="4" t="inlineStr">
+        <is>
+          <t>Boi de Madeira</t>
+        </is>
+      </c>
+      <c r="Y4" s="4" t="inlineStr">
+        <is>
+          <t>Bue di Legno</t>
+        </is>
+      </c>
+      <c r="Z4" s="4" t="inlineStr">
+        <is>
+          <t>Buey de Madera</t>
+        </is>
+      </c>
+      <c r="AA4" s="4" t="inlineStr">
+        <is>
+          <t>Модон үхэр</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="92" customHeight="1">
       <c r="A5" s="2" t="n">
@@ -874,15 +982,51 @@
       <c r="P5" s="4" t="inlineStr"/>
       <c r="Q5" s="4" t="inlineStr"/>
       <c r="R5" s="4" t="inlineStr"/>
-      <c r="S5" s="4" t="inlineStr"/>
-      <c r="T5" s="4" t="inlineStr"/>
-      <c r="U5" s="4" t="inlineStr"/>
-      <c r="V5" s="4" t="inlineStr"/>
-      <c r="W5" s="4" t="inlineStr"/>
-      <c r="X5" s="4" t="inlineStr"/>
-      <c r="Y5" s="4" t="inlineStr"/>
-      <c r="Z5" s="4" t="inlineStr"/>
-      <c r="AA5" s="4" t="inlineStr"/>
+      <c r="S5" s="4" t="inlineStr">
+        <is>
+          <t>Mafeisan</t>
+        </is>
+      </c>
+      <c r="T5" s="4" t="inlineStr">
+        <is>
+          <t>麻沸散</t>
+        </is>
+      </c>
+      <c r="U5" s="4" t="inlineStr">
+        <is>
+          <t>麻沸散</t>
+        </is>
+      </c>
+      <c r="V5" s="4" t="inlineStr">
+        <is>
+          <t>麻沸散</t>
+        </is>
+      </c>
+      <c r="W5" s="4" t="inlineStr">
+        <is>
+          <t>Mafeisan</t>
+        </is>
+      </c>
+      <c r="X5" s="4" t="inlineStr">
+        <is>
+          <t>Mafeisan</t>
+        </is>
+      </c>
+      <c r="Y5" s="4" t="inlineStr">
+        <is>
+          <t>Mafeisan</t>
+        </is>
+      </c>
+      <c r="Z5" s="4" t="inlineStr">
+        <is>
+          <t>Mafeisan</t>
+        </is>
+      </c>
+      <c r="AA5" s="4" t="inlineStr">
+        <is>
+          <t>Мафэйсань</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="92" customHeight="1">
       <c r="A6" s="2" t="n">
@@ -933,15 +1077,51 @@
       <c r="P6" s="4" t="inlineStr"/>
       <c r="Q6" s="4" t="inlineStr"/>
       <c r="R6" s="4" t="inlineStr"/>
-      <c r="S6" s="4" t="inlineStr"/>
-      <c r="T6" s="4" t="inlineStr"/>
-      <c r="U6" s="4" t="inlineStr"/>
-      <c r="V6" s="4" t="inlineStr"/>
-      <c r="W6" s="4" t="inlineStr"/>
-      <c r="X6" s="4" t="inlineStr"/>
-      <c r="Y6" s="4" t="inlineStr"/>
-      <c r="Z6" s="4" t="inlineStr"/>
-      <c r="AA6" s="4" t="inlineStr"/>
+      <c r="S6" s="4" t="inlineStr">
+        <is>
+          <t>Blue Satchel Book</t>
+        </is>
+      </c>
+      <c r="T6" s="4" t="inlineStr">
+        <is>
+          <t>青嚢書</t>
+        </is>
+      </c>
+      <c r="U6" s="4" t="inlineStr">
+        <is>
+          <t>青囊書</t>
+        </is>
+      </c>
+      <c r="V6" s="4" t="inlineStr">
+        <is>
+          <t>青囊书</t>
+        </is>
+      </c>
+      <c r="W6" s="4" t="inlineStr">
+        <is>
+          <t>Livro da Bolsa Azul</t>
+        </is>
+      </c>
+      <c r="X6" s="4" t="inlineStr">
+        <is>
+          <t>Livro da Bolsa Azul</t>
+        </is>
+      </c>
+      <c r="Y6" s="4" t="inlineStr">
+        <is>
+          <t>Libro della Borsa Blu</t>
+        </is>
+      </c>
+      <c r="Z6" s="4" t="inlineStr">
+        <is>
+          <t>Libro de la Bolsa Azul</t>
+        </is>
+      </c>
+      <c r="AA6" s="4" t="inlineStr">
+        <is>
+          <t>Хөх уутны ном</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="92" customHeight="1">
       <c r="A7" s="2" t="n">
@@ -992,15 +1172,51 @@
       <c r="P7" s="4" t="inlineStr"/>
       <c r="Q7" s="4" t="inlineStr"/>
       <c r="R7" s="4" t="inlineStr"/>
-      <c r="S7" s="4" t="inlineStr"/>
-      <c r="T7" s="4" t="inlineStr"/>
-      <c r="U7" s="4" t="inlineStr"/>
-      <c r="V7" s="4" t="inlineStr"/>
-      <c r="W7" s="4" t="inlineStr"/>
-      <c r="X7" s="4" t="inlineStr"/>
-      <c r="Y7" s="4" t="inlineStr"/>
-      <c r="Z7" s="4" t="inlineStr"/>
-      <c r="AA7" s="4" t="inlineStr"/>
+      <c r="S7" s="4" t="inlineStr">
+        <is>
+          <t>Taiping Arts</t>
+        </is>
+      </c>
+      <c r="T7" s="4" t="inlineStr">
+        <is>
+          <t>太平要術</t>
+        </is>
+      </c>
+      <c r="U7" s="4" t="inlineStr">
+        <is>
+          <t>太平要術</t>
+        </is>
+      </c>
+      <c r="V7" s="4" t="inlineStr">
+        <is>
+          <t>太平要术</t>
+        </is>
+      </c>
+      <c r="W7" s="4" t="inlineStr">
+        <is>
+          <t>Artes de Taiping</t>
+        </is>
+      </c>
+      <c r="X7" s="4" t="inlineStr">
+        <is>
+          <t>Artes de Taiping</t>
+        </is>
+      </c>
+      <c r="Y7" s="4" t="inlineStr">
+        <is>
+          <t>Arti di Taiping</t>
+        </is>
+      </c>
+      <c r="Z7" s="4" t="inlineStr">
+        <is>
+          <t>Artes de Taiping</t>
+        </is>
+      </c>
+      <c r="AA7" s="4" t="inlineStr">
+        <is>
+          <t>Тайпиний эрдэм</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="92" customHeight="1">
       <c r="A8" s="2" t="n">
@@ -1051,15 +1267,51 @@
       <c r="P8" s="4" t="inlineStr"/>
       <c r="Q8" s="4" t="inlineStr"/>
       <c r="R8" s="4" t="inlineStr"/>
-      <c r="S8" s="4" t="inlineStr"/>
-      <c r="T8" s="4" t="inlineStr"/>
-      <c r="U8" s="4" t="inlineStr"/>
-      <c r="V8" s="4" t="inlineStr"/>
-      <c r="W8" s="4" t="inlineStr"/>
-      <c r="X8" s="4" t="inlineStr"/>
-      <c r="Y8" s="4" t="inlineStr"/>
-      <c r="Z8" s="4" t="inlineStr"/>
-      <c r="AA8" s="4" t="inlineStr"/>
+      <c r="S8" s="4" t="inlineStr">
+        <is>
+          <t>Six Secret Teachings</t>
+        </is>
+      </c>
+      <c r="T8" s="4" t="inlineStr">
+        <is>
+          <t>六韜三略</t>
+        </is>
+      </c>
+      <c r="U8" s="4" t="inlineStr">
+        <is>
+          <t>六韜三略</t>
+        </is>
+      </c>
+      <c r="V8" s="4" t="inlineStr">
+        <is>
+          <t>六韬三略</t>
+        </is>
+      </c>
+      <c r="W8" s="4" t="inlineStr">
+        <is>
+          <t>Seis Ensinamentos Secretos</t>
+        </is>
+      </c>
+      <c r="X8" s="4" t="inlineStr">
+        <is>
+          <t>Seis Ensinamentos Secretos</t>
+        </is>
+      </c>
+      <c r="Y8" s="4" t="inlineStr">
+        <is>
+          <t>Sei Insegnamenti Segreti</t>
+        </is>
+      </c>
+      <c r="Z8" s="4" t="inlineStr">
+        <is>
+          <t>Seis Enseñanzas Secretas</t>
+        </is>
+      </c>
+      <c r="AA8" s="4" t="inlineStr">
+        <is>
+          <t>Зургаан сургаал</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="92" customHeight="1">
       <c r="A9" s="2" t="n">
@@ -1110,15 +1362,51 @@
       <c r="P9" s="4" t="inlineStr"/>
       <c r="Q9" s="4" t="inlineStr"/>
       <c r="R9" s="4" t="inlineStr"/>
-      <c r="S9" s="4" t="inlineStr"/>
-      <c r="T9" s="4" t="inlineStr"/>
-      <c r="U9" s="4" t="inlineStr"/>
-      <c r="V9" s="4" t="inlineStr"/>
-      <c r="W9" s="4" t="inlineStr"/>
-      <c r="X9" s="4" t="inlineStr"/>
-      <c r="Y9" s="4" t="inlineStr"/>
-      <c r="Z9" s="4" t="inlineStr"/>
-      <c r="AA9" s="4" t="inlineStr"/>
+      <c r="S9" s="4" t="inlineStr">
+        <is>
+          <t>The Art of War</t>
+        </is>
+      </c>
+      <c r="T9" s="4" t="inlineStr">
+        <is>
+          <t>孫子兵法書</t>
+        </is>
+      </c>
+      <c r="U9" s="4" t="inlineStr">
+        <is>
+          <t>孫子兵法書</t>
+        </is>
+      </c>
+      <c r="V9" s="4" t="inlineStr">
+        <is>
+          <t>孙子兵法书</t>
+        </is>
+      </c>
+      <c r="W9" s="4" t="inlineStr">
+        <is>
+          <t>A Arte da Guerra</t>
+        </is>
+      </c>
+      <c r="X9" s="4" t="inlineStr">
+        <is>
+          <t>A Arte da Guerra</t>
+        </is>
+      </c>
+      <c r="Y9" s="4" t="inlineStr">
+        <is>
+          <t>L'arte della guerra</t>
+        </is>
+      </c>
+      <c r="Z9" s="4" t="inlineStr">
+        <is>
+          <t>El arte de la guerra</t>
+        </is>
+      </c>
+      <c r="AA9" s="4" t="inlineStr">
+        <is>
+          <t>Дайны урлаг</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="92" customHeight="1">
       <c r="A10" s="2" t="n">
@@ -1169,15 +1457,51 @@
       <c r="P10" s="4" t="inlineStr"/>
       <c r="Q10" s="4" t="inlineStr"/>
       <c r="R10" s="4" t="inlineStr"/>
-      <c r="S10" s="4" t="inlineStr"/>
-      <c r="T10" s="4" t="inlineStr"/>
-      <c r="U10" s="4" t="inlineStr"/>
-      <c r="V10" s="4" t="inlineStr"/>
-      <c r="W10" s="4" t="inlineStr"/>
-      <c r="X10" s="4" t="inlineStr"/>
-      <c r="Y10" s="4" t="inlineStr"/>
-      <c r="Z10" s="4" t="inlineStr"/>
-      <c r="AA10" s="4" t="inlineStr"/>
+      <c r="S10" s="4" t="inlineStr">
+        <is>
+          <t>Ferghana Horse</t>
+        </is>
+      </c>
+      <c r="T10" s="4" t="inlineStr">
+        <is>
+          <t>大宛馬</t>
+        </is>
+      </c>
+      <c r="U10" s="4" t="inlineStr">
+        <is>
+          <t>大宛馬</t>
+        </is>
+      </c>
+      <c r="V10" s="4" t="inlineStr">
+        <is>
+          <t>大宛马</t>
+        </is>
+      </c>
+      <c r="W10" s="4" t="inlineStr">
+        <is>
+          <t>Cavalo de Ferghana</t>
+        </is>
+      </c>
+      <c r="X10" s="4" t="inlineStr">
+        <is>
+          <t>Cavalo de Ferghana</t>
+        </is>
+      </c>
+      <c r="Y10" s="4" t="inlineStr">
+        <is>
+          <t>Cavallo di Fergana</t>
+        </is>
+      </c>
+      <c r="Z10" s="4" t="inlineStr">
+        <is>
+          <t>Caballo de Fergana</t>
+        </is>
+      </c>
+      <c r="AA10" s="4" t="inlineStr">
+        <is>
+          <t>Фергана морь</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="92" customHeight="1">
       <c r="A11" s="2" t="n">
@@ -1228,15 +1552,51 @@
       <c r="P11" s="4" t="inlineStr"/>
       <c r="Q11" s="4" t="inlineStr"/>
       <c r="R11" s="4" t="inlineStr"/>
-      <c r="S11" s="4" t="inlineStr"/>
-      <c r="T11" s="4" t="inlineStr"/>
-      <c r="U11" s="4" t="inlineStr"/>
-      <c r="V11" s="4" t="inlineStr"/>
-      <c r="W11" s="4" t="inlineStr"/>
-      <c r="X11" s="4" t="inlineStr"/>
-      <c r="Y11" s="4" t="inlineStr"/>
-      <c r="Z11" s="4" t="inlineStr"/>
-      <c r="AA11" s="4" t="inlineStr"/>
+      <c r="S11" s="4" t="inlineStr">
+        <is>
+          <t>Dilu</t>
+        </is>
+      </c>
+      <c r="T11" s="4" t="inlineStr">
+        <is>
+          <t>的盧</t>
+        </is>
+      </c>
+      <c r="U11" s="4" t="inlineStr">
+        <is>
+          <t>的盧</t>
+        </is>
+      </c>
+      <c r="V11" s="4" t="inlineStr">
+        <is>
+          <t>的卢</t>
+        </is>
+      </c>
+      <c r="W11" s="4" t="inlineStr">
+        <is>
+          <t>Dilu</t>
+        </is>
+      </c>
+      <c r="X11" s="4" t="inlineStr">
+        <is>
+          <t>Dilu</t>
+        </is>
+      </c>
+      <c r="Y11" s="4" t="inlineStr">
+        <is>
+          <t>Dilu</t>
+        </is>
+      </c>
+      <c r="Z11" s="4" t="inlineStr">
+        <is>
+          <t>Dilu</t>
+        </is>
+      </c>
+      <c r="AA11" s="4" t="inlineStr">
+        <is>
+          <t>Дилү</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="92" customHeight="1">
       <c r="A12" s="2" t="n">
@@ -1287,15 +1647,51 @@
       <c r="P12" s="4" t="inlineStr"/>
       <c r="Q12" s="4" t="inlineStr"/>
       <c r="R12" s="4" t="inlineStr"/>
-      <c r="S12" s="4" t="inlineStr"/>
-      <c r="T12" s="4" t="inlineStr"/>
-      <c r="U12" s="4" t="inlineStr"/>
-      <c r="V12" s="4" t="inlineStr"/>
-      <c r="W12" s="4" t="inlineStr"/>
-      <c r="X12" s="4" t="inlineStr"/>
-      <c r="Y12" s="4" t="inlineStr"/>
-      <c r="Z12" s="4" t="inlineStr"/>
-      <c r="AA12" s="4" t="inlineStr"/>
+      <c r="S12" s="4" t="inlineStr">
+        <is>
+          <t>Jueying</t>
+        </is>
+      </c>
+      <c r="T12" s="4" t="inlineStr">
+        <is>
+          <t>絶影</t>
+        </is>
+      </c>
+      <c r="U12" s="4" t="inlineStr">
+        <is>
+          <t>絕影</t>
+        </is>
+      </c>
+      <c r="V12" s="4" t="inlineStr">
+        <is>
+          <t>绝影</t>
+        </is>
+      </c>
+      <c r="W12" s="4" t="inlineStr">
+        <is>
+          <t>Jueying</t>
+        </is>
+      </c>
+      <c r="X12" s="4" t="inlineStr">
+        <is>
+          <t>Jueying</t>
+        </is>
+      </c>
+      <c r="Y12" s="4" t="inlineStr">
+        <is>
+          <t>Jueying</t>
+        </is>
+      </c>
+      <c r="Z12" s="4" t="inlineStr">
+        <is>
+          <t>Jueying</t>
+        </is>
+      </c>
+      <c r="AA12" s="4" t="inlineStr">
+        <is>
+          <t>Жүэин</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="92" customHeight="1">
       <c r="A13" s="2" t="n">
@@ -1346,15 +1742,51 @@
       <c r="P13" s="4" t="inlineStr"/>
       <c r="Q13" s="4" t="inlineStr"/>
       <c r="R13" s="4" t="inlineStr"/>
-      <c r="S13" s="4" t="inlineStr"/>
-      <c r="T13" s="4" t="inlineStr"/>
-      <c r="U13" s="4" t="inlineStr"/>
-      <c r="V13" s="4" t="inlineStr"/>
-      <c r="W13" s="4" t="inlineStr"/>
-      <c r="X13" s="4" t="inlineStr"/>
-      <c r="Y13" s="4" t="inlineStr"/>
-      <c r="Z13" s="4" t="inlineStr"/>
-      <c r="AA13" s="4" t="inlineStr"/>
+      <c r="S13" s="4" t="inlineStr">
+        <is>
+          <t>Red Hare</t>
+        </is>
+      </c>
+      <c r="T13" s="4" t="inlineStr">
+        <is>
+          <t>赤兎馬</t>
+        </is>
+      </c>
+      <c r="U13" s="4" t="inlineStr">
+        <is>
+          <t>赤兔馬</t>
+        </is>
+      </c>
+      <c r="V13" s="4" t="inlineStr">
+        <is>
+          <t>赤兔马</t>
+        </is>
+      </c>
+      <c r="W13" s="4" t="inlineStr">
+        <is>
+          <t>Lebre Vermelha</t>
+        </is>
+      </c>
+      <c r="X13" s="4" t="inlineStr">
+        <is>
+          <t>Lebre Vermelha</t>
+        </is>
+      </c>
+      <c r="Y13" s="4" t="inlineStr">
+        <is>
+          <t>Lepre Rossa</t>
+        </is>
+      </c>
+      <c r="Z13" s="4" t="inlineStr">
+        <is>
+          <t>Liebre Roja</t>
+        </is>
+      </c>
+      <c r="AA13" s="4" t="inlineStr">
+        <is>
+          <t>Улаан туулай</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="92" customHeight="1">
       <c r="A14" s="2" t="n">
@@ -1405,15 +1837,51 @@
       <c r="P14" s="4" t="inlineStr"/>
       <c r="Q14" s="4" t="inlineStr"/>
       <c r="R14" s="4" t="inlineStr"/>
-      <c r="S14" s="4" t="inlineStr"/>
-      <c r="T14" s="4" t="inlineStr"/>
-      <c r="U14" s="4" t="inlineStr"/>
-      <c r="V14" s="4" t="inlineStr"/>
-      <c r="W14" s="4" t="inlineStr"/>
-      <c r="X14" s="4" t="inlineStr"/>
-      <c r="Y14" s="4" t="inlineStr"/>
-      <c r="Z14" s="4" t="inlineStr"/>
-      <c r="AA14" s="4" t="inlineStr"/>
+      <c r="S14" s="4" t="inlineStr">
+        <is>
+          <t>Scout Rider</t>
+        </is>
+      </c>
+      <c r="T14" s="4" t="inlineStr">
+        <is>
+          <t>斥候騎</t>
+        </is>
+      </c>
+      <c r="U14" s="4" t="inlineStr">
+        <is>
+          <t>斥候騎</t>
+        </is>
+      </c>
+      <c r="V14" s="4" t="inlineStr">
+        <is>
+          <t>斥候骑</t>
+        </is>
+      </c>
+      <c r="W14" s="4" t="inlineStr">
+        <is>
+          <t>Batedor Montado</t>
+        </is>
+      </c>
+      <c r="X14" s="4" t="inlineStr">
+        <is>
+          <t>Batedor Montado</t>
+        </is>
+      </c>
+      <c r="Y14" s="4" t="inlineStr">
+        <is>
+          <t>Esploratore a Cavallo</t>
+        </is>
+      </c>
+      <c r="Z14" s="4" t="inlineStr">
+        <is>
+          <t>Explorador Montado</t>
+        </is>
+      </c>
+      <c r="AA14" s="4" t="inlineStr">
+        <is>
+          <t>Морьт тагнуул</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="92" customHeight="1">
       <c r="A15" s="2" t="n">
@@ -1464,15 +1932,51 @@
       <c r="P15" s="4" t="inlineStr"/>
       <c r="Q15" s="4" t="inlineStr"/>
       <c r="R15" s="4" t="inlineStr"/>
-      <c r="S15" s="4" t="inlineStr"/>
-      <c r="T15" s="4" t="inlineStr"/>
-      <c r="U15" s="4" t="inlineStr"/>
-      <c r="V15" s="4" t="inlineStr"/>
-      <c r="W15" s="4" t="inlineStr"/>
-      <c r="X15" s="4" t="inlineStr"/>
-      <c r="Y15" s="4" t="inlineStr"/>
-      <c r="Z15" s="4" t="inlineStr"/>
-      <c r="AA15" s="4" t="inlineStr"/>
+      <c r="S15" s="4" t="inlineStr">
+        <is>
+          <t>Explosive</t>
+        </is>
+      </c>
+      <c r="T15" s="4" t="inlineStr">
+        <is>
+          <t>爆薬</t>
+        </is>
+      </c>
+      <c r="U15" s="4" t="inlineStr">
+        <is>
+          <t>爆藥</t>
+        </is>
+      </c>
+      <c r="V15" s="4" t="inlineStr">
+        <is>
+          <t>爆药</t>
+        </is>
+      </c>
+      <c r="W15" s="4" t="inlineStr">
+        <is>
+          <t>Explosivo</t>
+        </is>
+      </c>
+      <c r="X15" s="4" t="inlineStr">
+        <is>
+          <t>Explosivo</t>
+        </is>
+      </c>
+      <c r="Y15" s="4" t="inlineStr">
+        <is>
+          <t>Esplosivo</t>
+        </is>
+      </c>
+      <c r="Z15" s="4" t="inlineStr">
+        <is>
+          <t>Explosivo</t>
+        </is>
+      </c>
+      <c r="AA15" s="4" t="inlineStr">
+        <is>
+          <t>Тэсрэх бодис</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="92" customHeight="1">
       <c r="A16" s="2" t="n">
@@ -1523,15 +2027,51 @@
       <c r="P16" s="4" t="inlineStr"/>
       <c r="Q16" s="4" t="inlineStr"/>
       <c r="R16" s="4" t="inlineStr"/>
-      <c r="S16" s="4" t="inlineStr"/>
-      <c r="T16" s="4" t="inlineStr"/>
-      <c r="U16" s="4" t="inlineStr"/>
-      <c r="V16" s="4" t="inlineStr"/>
-      <c r="W16" s="4" t="inlineStr"/>
-      <c r="X16" s="4" t="inlineStr"/>
-      <c r="Y16" s="4" t="inlineStr"/>
-      <c r="Z16" s="4" t="inlineStr"/>
-      <c r="AA16" s="4" t="inlineStr"/>
+      <c r="S16" s="4" t="inlineStr">
+        <is>
+          <t>Feather Fan</t>
+        </is>
+      </c>
+      <c r="T16" s="4" t="inlineStr">
+        <is>
+          <t>羽扇</t>
+        </is>
+      </c>
+      <c r="U16" s="4" t="inlineStr">
+        <is>
+          <t>羽扇</t>
+        </is>
+      </c>
+      <c r="V16" s="4" t="inlineStr">
+        <is>
+          <t>羽扇</t>
+        </is>
+      </c>
+      <c r="W16" s="4" t="inlineStr">
+        <is>
+          <t>Leque de Penas</t>
+        </is>
+      </c>
+      <c r="X16" s="4" t="inlineStr">
+        <is>
+          <t>Leque de Penas</t>
+        </is>
+      </c>
+      <c r="Y16" s="4" t="inlineStr">
+        <is>
+          <t>Ventaglio di Piume</t>
+        </is>
+      </c>
+      <c r="Z16" s="4" t="inlineStr">
+        <is>
+          <t>Abanico de Plumas</t>
+        </is>
+      </c>
+      <c r="AA16" s="4" t="inlineStr">
+        <is>
+          <t>Өдөн сэнс</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="92" customHeight="1">
       <c r="A17" s="2" t="n">
@@ -1582,15 +2122,51 @@
       <c r="P17" s="4" t="inlineStr"/>
       <c r="Q17" s="4" t="inlineStr"/>
       <c r="R17" s="4" t="inlineStr"/>
-      <c r="S17" s="4" t="inlineStr"/>
-      <c r="T17" s="4" t="inlineStr"/>
-      <c r="U17" s="4" t="inlineStr"/>
-      <c r="V17" s="4" t="inlineStr"/>
-      <c r="W17" s="4" t="inlineStr"/>
-      <c r="X17" s="4" t="inlineStr"/>
-      <c r="Y17" s="4" t="inlineStr"/>
-      <c r="Z17" s="4" t="inlineStr"/>
-      <c r="AA17" s="4" t="inlineStr"/>
+      <c r="S17" s="4" t="inlineStr">
+        <is>
+          <t>Command Flag</t>
+        </is>
+      </c>
+      <c r="T17" s="4" t="inlineStr">
+        <is>
+          <t>令旗</t>
+        </is>
+      </c>
+      <c r="U17" s="4" t="inlineStr">
+        <is>
+          <t>令旗</t>
+        </is>
+      </c>
+      <c r="V17" s="4" t="inlineStr">
+        <is>
+          <t>令旗</t>
+        </is>
+      </c>
+      <c r="W17" s="4" t="inlineStr">
+        <is>
+          <t>Bandeira de Comando</t>
+        </is>
+      </c>
+      <c r="X17" s="4" t="inlineStr">
+        <is>
+          <t>Bandeira de Comando</t>
+        </is>
+      </c>
+      <c r="Y17" s="4" t="inlineStr">
+        <is>
+          <t>Bandiera di Comando</t>
+        </is>
+      </c>
+      <c r="Z17" s="4" t="inlineStr">
+        <is>
+          <t>Bandera de Mando</t>
+        </is>
+      </c>
+      <c r="AA17" s="4" t="inlineStr">
+        <is>
+          <t>Тушаалын туг</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
